--- a/Bauteillisten/Bestellliste_DigiKey_V7.xlsx
+++ b/Bauteillisten/Bestellliste_DigiKey_V7.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janne\Documents\GitHub\active-balancing\Bauteillisten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Documents\Uni\Semester 6\Projektarbeit\active-balancing\Bauteillisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E95AF628-EB02-444E-BA30-913DBC957BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EDA0BC-7660-4680-AFE6-18A26712330F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -518,7 +531,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -527,6 +540,17 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -549,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -558,6 +582,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -576,9 +602,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -616,7 +642,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -722,7 +748,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -864,7 +890,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -873,20 +899,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="6.77734375" customWidth="1"/>
-    <col min="3" max="3" width="33.77734375" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="43.21875" customWidth="1"/>
-    <col min="6" max="6" width="18.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
+    <col min="1" max="2" width="6.81640625" customWidth="1"/>
+    <col min="3" max="3" width="33.81640625" customWidth="1"/>
+    <col min="4" max="4" width="29.6328125" customWidth="1"/>
+    <col min="5" max="5" width="43.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.90625" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" customWidth="1"/>
+    <col min="8" max="8" width="21.54296875" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -900,7 +926,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -932,7 +958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -945,7 +971,7 @@
       <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="2">
@@ -961,7 +987,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -971,10 +997,10 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="2">
@@ -990,7 +1016,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1000,10 +1026,10 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="2">
@@ -1019,7 +1045,7 @@
         <v>6.32</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1029,10 +1055,10 @@
       <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="2">
@@ -1048,7 +1074,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1061,7 +1087,7 @@
       <c r="D7" s="2">
         <v>865080342006</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="2">
@@ -1077,7 +1103,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1090,7 +1116,7 @@
       <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G8" s="2">
@@ -1106,7 +1132,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1116,10 +1142,10 @@
       <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="2">
@@ -1135,7 +1161,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1145,10 +1171,10 @@
       <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="2">
@@ -1164,7 +1190,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1174,10 +1200,10 @@
       <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G11" s="2">
@@ -1193,7 +1219,7 @@
         <v>33.79</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1206,7 +1232,7 @@
       <c r="D12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="6" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="2">
@@ -1222,7 +1248,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1232,10 +1258,10 @@
       <c r="C13" t="s">
         <v>40</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="2">
@@ -1251,7 +1277,7 @@
         <v>32.72</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1264,7 +1290,7 @@
       <c r="D14" t="s">
         <v>44</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G14" s="2">
@@ -1280,7 +1306,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1290,10 +1316,10 @@
       <c r="C15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G15" s="2">
@@ -1309,7 +1335,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1319,10 +1345,10 @@
       <c r="C16" t="s">
         <v>49</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="6" t="s">
         <v>51</v>
       </c>
       <c r="G16" s="2">
@@ -1338,7 +1364,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1351,7 +1377,7 @@
       <c r="D17" t="s">
         <v>53</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="6" t="s">
         <v>54</v>
       </c>
       <c r="G17" s="2">
@@ -1367,7 +1393,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1377,10 +1403,10 @@
       <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="6" t="s">
         <v>57</v>
       </c>
       <c r="G18" s="2">
@@ -1396,7 +1422,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1406,10 +1432,10 @@
       <c r="C19" t="s">
         <v>58</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G19" s="2">
@@ -1425,7 +1451,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1438,7 +1464,7 @@
       <c r="D20" t="s">
         <v>62</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G20" s="2">
@@ -1454,7 +1480,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1467,7 +1493,7 @@
       <c r="D21" t="s">
         <v>65</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="6" t="s">
         <v>66</v>
       </c>
       <c r="G21" s="2">
@@ -1483,7 +1509,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1493,10 +1519,10 @@
       <c r="C22" t="s">
         <v>67</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="6" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2">
@@ -1512,7 +1538,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1522,10 +1548,10 @@
       <c r="C23" t="s">
         <v>70</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="6" t="s">
         <v>72</v>
       </c>
       <c r="G23" s="2">
@@ -1541,7 +1567,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1551,10 +1577,10 @@
       <c r="C24" t="s">
         <v>73</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="6" t="s">
         <v>75</v>
       </c>
       <c r="G24" s="2">
@@ -1570,7 +1596,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1580,10 +1606,10 @@
       <c r="C25" t="s">
         <v>76</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="6" t="s">
         <v>78</v>
       </c>
       <c r="G25" s="2">
@@ -1599,7 +1625,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1609,10 +1635,10 @@
       <c r="C26" t="s">
         <v>79</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="6" t="s">
         <v>81</v>
       </c>
       <c r="G26" s="2">
@@ -1628,7 +1654,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -1638,10 +1664,10 @@
       <c r="C27" t="s">
         <v>82</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="6" t="s">
         <v>84</v>
       </c>
       <c r="G27" s="2">
@@ -1657,7 +1683,7 @@
         <v>6.28</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -1667,10 +1693,10 @@
       <c r="C28" t="s">
         <v>85</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="6" t="s">
         <v>87</v>
       </c>
       <c r="G28" s="2">
@@ -1686,7 +1712,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -1696,10 +1722,10 @@
       <c r="C29" t="s">
         <v>88</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="6" t="s">
         <v>90</v>
       </c>
       <c r="G29" s="2">
@@ -1715,7 +1741,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -1725,10 +1751,10 @@
       <c r="C30" t="s">
         <v>91</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="6" t="s">
         <v>93</v>
       </c>
       <c r="G30" s="2">
@@ -1744,7 +1770,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -1754,10 +1780,10 @@
       <c r="C31" t="s">
         <v>94</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="6" t="s">
         <v>96</v>
       </c>
       <c r="G31" s="2">
@@ -1773,7 +1799,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -1786,7 +1812,7 @@
       <c r="D32" t="s">
         <v>98</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="6" t="s">
         <v>99</v>
       </c>
       <c r="G32" s="2">
@@ -1802,7 +1828,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -1812,10 +1838,10 @@
       <c r="C33" t="s">
         <v>100</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="6" t="s">
         <v>102</v>
       </c>
       <c r="G33" s="2">
@@ -1831,7 +1857,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -1841,10 +1867,10 @@
       <c r="C34" t="s">
         <v>103</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="6" t="s">
         <v>105</v>
       </c>
       <c r="G34" s="2">
@@ -1860,7 +1886,7 @@
         <v>10.54</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -1870,10 +1896,10 @@
       <c r="C35" t="s">
         <v>106</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="6" t="s">
         <v>108</v>
       </c>
       <c r="G35" s="2">
@@ -1889,7 +1915,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -1899,10 +1925,10 @@
       <c r="C36" t="s">
         <v>109</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="6" t="s">
         <v>111</v>
       </c>
       <c r="G36" s="2">
@@ -1918,7 +1944,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -1928,10 +1954,10 @@
       <c r="C37" t="s">
         <v>112</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="6" t="s">
         <v>114</v>
       </c>
       <c r="G37" s="2">
@@ -1947,7 +1973,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -1957,10 +1983,10 @@
       <c r="C38" t="s">
         <v>115</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="6" t="s">
         <v>117</v>
       </c>
       <c r="G38" s="2">
@@ -1976,7 +2002,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -2005,7 +2031,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -2034,7 +2060,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -2063,7 +2089,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -2073,10 +2099,10 @@
       <c r="C42" t="s">
         <v>127</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="6" t="s">
         <v>129</v>
       </c>
       <c r="G42" s="2">
@@ -2092,7 +2118,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -2105,7 +2131,7 @@
       <c r="D43" t="s">
         <v>131</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="6" t="s">
         <v>132</v>
       </c>
       <c r="G43" s="2">
@@ -2121,7 +2147,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -2131,10 +2157,10 @@
       <c r="C44" t="s">
         <v>133</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="6" t="s">
         <v>135</v>
       </c>
       <c r="G44" s="2">
@@ -2150,7 +2176,7 @@
         <v>12.52</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -2163,7 +2189,7 @@
       <c r="D45" t="s">
         <v>137</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="6" t="s">
         <v>138</v>
       </c>
       <c r="G45" s="2">
@@ -2179,7 +2205,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -2189,10 +2215,10 @@
       <c r="C46" t="s">
         <v>139</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="6" t="s">
         <v>141</v>
       </c>
       <c r="G46" s="2">
@@ -2208,7 +2234,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -2218,10 +2244,10 @@
       <c r="C47" t="s">
         <v>142</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="6" t="s">
         <v>144</v>
       </c>
       <c r="G47" s="2">
@@ -2237,7 +2263,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -2247,10 +2273,10 @@
       <c r="C48" t="s">
         <v>145</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="6" t="s">
         <v>147</v>
       </c>
       <c r="G48" s="2">
@@ -2266,7 +2292,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -2279,7 +2305,7 @@
       <c r="D49" t="s">
         <v>149</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="6" t="s">
         <v>150</v>
       </c>
       <c r="G49" s="2">
@@ -2295,7 +2321,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -2305,10 +2331,10 @@
       <c r="C50" t="s">
         <v>151</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="6" t="s">
         <v>153</v>
       </c>
       <c r="G50" s="2">
@@ -2324,7 +2350,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -2337,7 +2363,7 @@
       <c r="D51" s="2">
         <v>691137710002</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="6" t="s">
         <v>155</v>
       </c>
       <c r="G51" s="2">
@@ -2353,7 +2379,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -2366,7 +2392,7 @@
       <c r="D52" s="2">
         <v>691137710003</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" s="6" t="s">
         <v>157</v>
       </c>
       <c r="G52" s="2">
@@ -2382,7 +2408,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -2395,7 +2421,7 @@
       <c r="D53" t="s">
         <v>159</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" s="6" t="s">
         <v>160</v>
       </c>
       <c r="G53" s="2">
@@ -2411,7 +2437,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -2421,10 +2447,10 @@
       <c r="C54" t="s">
         <v>161</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" s="6" t="s">
         <v>163</v>
       </c>
       <c r="G54" s="2">
